--- a/CB_HSI_MAPPING/testing_final/Input/HSI_template_generated_by_sheet.xlsx
+++ b/CB_HSI_MAPPING/testing_final/Input/HSI_template_generated_by_sheet.xlsx
@@ -23224,8 +23224,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x010100F4ECDE3992A08C4AB27EAAF617A05967" ma:contentTypeVersion="12" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="3dd12f097a664388af7c7ed37b7f1677">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="455088e1-af34-4927-a3f0-bdce59540293" xmlns:ns3="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="67c07fb3e546643451b6621acfe4996e" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F4ECDE3992A08C4AB27EAAF617A05967" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9683c085a59988fd2dc84fe522921e1c">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="455088e1-af34-4927-a3f0-bdce59540293" xmlns:ns3="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7184c417cebe2c46bf9076e6fd8b1060" ns2:_="" ns3:_="">
     <xsd:import namespace="455088e1-af34-4927-a3f0-bdce59540293"/>
     <xsd:import namespace="f4ecdb93-bc7f-4438-8c77-236ab96c18a9"/>
     <xsd:element name="properties">
@@ -23245,6 +23245,12 @@
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:testStatus" minOccurs="0"/>
+                <xsd:element ref="ns3:PrimeClassificationStatus" minOccurs="0"/>
+                <xsd:element ref="ns3:PrimeClassificationStatusDetails" minOccurs="0"/>
+                <xsd:element ref="ns3:PrimeLastClassified" minOccurs="0"/>
+                <xsd:element ref="ns3:PrimeCorrectedByUser" minOccurs="0"/>
+                <xsd:element ref="ns3:PrimeAutofillMeta" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -23275,7 +23281,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="图像标记" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="61535f45-074a-4eaf-b5ce-0ad645dc0277" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="61535f45-074a-4eaf-b5ce-0ad645dc0277" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -23309,6 +23315,18 @@
         <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="testStatus" ma:index="20" nillable="true" ma:displayName="Test status" ma:description="Summarizes overall test outcome so failed or mixed-result files can be found quickly." ma:internalName="testStatus">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="Pass"/>
+          <xsd:enumeration value="Fail"/>
+          <xsd:enumeration value="Error"/>
+          <xsd:enumeration value="Skipped"/>
+          <xsd:enumeration value="Mixed"/>
+          <xsd:enumeration value="Not found"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -23324,6 +23342,33 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
+    <xsd:element name="PrimeClassificationStatus" ma:index="21" nillable="true" ma:displayName="Processing status" ma:internalName="PrimeClassificationStatus">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="PrimeClassificationStatusDetails" ma:index="22" nillable="true" ma:displayName="Processing details" ma:internalName="PrimeClassificationStatusDetails">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="PrimeLastClassified" ma:index="23" nillable="true" ma:displayName="Processed" ma:internalName="PrimeLastClassified">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="PrimeCorrectedByUser" ma:index="24" nillable="true" ma:displayName="Corrected" ma:internalName="PrimeCorrectedByUser">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Boolean"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="PrimeAutofillMeta" ma:index="25" nillable="true" ma:displayName="Autofill Meta" ma:hidden="true" ma:internalName="PrimeAutofillMeta">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
     <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
@@ -23334,8 +23379,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="内容类型"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="标题"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -23440,12 +23485,18 @@
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
     <TaxCatchAll xmlns="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" xsi:nil="true"/>
+    <PrimeCorrectedByUser xmlns="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" xsi:nil="true"/>
+    <testStatus xmlns="455088e1-af34-4927-a3f0-bdce59540293" xsi:nil="true"/>
+    <PrimeClassificationStatusDetails xmlns="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" xsi:nil="true"/>
+    <PrimeClassificationStatus xmlns="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" xsi:nil="true"/>
+    <PrimeLastClassified xmlns="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" xsi:nil="true"/>
+    <PrimeAutofillMeta xmlns="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA4EA8DB-3F79-42A7-91B7-0F981001FA9C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4A6508F-4126-4709-A781-F3B1E3CF8220}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
